--- a/data/RetroVault_GS_Games_全量匯入檔.xlsx
+++ b/data/RetroVault_GS_Games_全量匯入檔.xlsx
@@ -856,7 +856,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/9501cf61-17bf-41fb-a840-9ad7d8ad6963.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/9501cf61-17bf-41fb-a840-9ad7d8ad6963.png</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr"/>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/045b85dd-e230-4809-80de-9145858621ec.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/045b85dd-e230-4809-80de-9145858621ec.png</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/d6dfb20b-429c-4830-8c92-d83036382b3a.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/d6dfb20b-429c-4830-8c92-d83036382b3a.png</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/ab003ef9-e5c0-4eea-940c-d8c6f20b218f.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/ab003ef9-e5c0-4eea-940c-d8c6f20b218f.jpg</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/95c5c000-460d-469d-943a-ba8b2b849aff.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/95c5c000-460d-469d-943a-ba8b2b849aff.jpg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/da74e1cf-0ed1-4d29-830f-26d652c86ce2.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/da74e1cf-0ed1-4d29-830f-26d652c86ce2.png</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/16a9b646-6264-48f5-bc9f-abc90bea4788.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/16a9b646-6264-48f5-bc9f-abc90bea4788.jpg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/5ed1e558-92d2-4baa-8946-28ea843da344.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/5ed1e558-92d2-4baa-8946-28ea843da344.png</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/ecb3020f-a139-412d-a417-81493f019841.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/ecb3020f-a139-412d-a417-81493f019841.jpg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/9d83bee8-4ba8-4bb8-be82-3115eebfe2fd.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/9d83bee8-4ba8-4bb8-be82-3115eebfe2fd.jpg</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/70ed527e-14dc-43fd-b7b6-8c655f2563eb.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/70ed527e-14dc-43fd-b7b6-8c655f2563eb.jpg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/93d0753b-cf8c-4c5e-9996-7c9b1020bb22.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/93d0753b-cf8c-4c5e-9996-7c9b1020bb22.jpg</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr"/>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/f2bd9be0-5908-4ddc-810b-3d995f018fec.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/f2bd9be0-5908-4ddc-810b-3d995f018fec.jpg</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr"/>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/8fb46976-74f0-4d66-bcfe-d8ec79631729.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/8fb46976-74f0-4d66-bcfe-d8ec79631729.jpg</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/bc9d3dba-0221-4a10-ab7f-3e59975c40c2.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/bc9d3dba-0221-4a10-ab7f-3e59975c40c2.jpg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/93240dc8-6979-432c-ab21-ed2bb3280412.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/93240dc8-6979-432c-ab21-ed2bb3280412.jpg</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/6d4a0648-4be0-46d9-90ff-3008c95b4ddf.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/6d4a0648-4be0-46d9-90ff-3008c95b4ddf.jpg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/a3c1d6b7-ebd5-49da-8802-695130dccdfc.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/a3c1d6b7-ebd5-49da-8802-695130dccdfc.png</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr"/>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/7140acbc-d4c1-448f-979e-31a945d6bd26.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/7140acbc-d4c1-448f-979e-31a945d6bd26.png</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr"/>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/ad489cf3-805b-4951-aa3d-6a32327d9bbb.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/ad489cf3-805b-4951-aa3d-6a32327d9bbb.jpg</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/108e5fc2-7823-42c3-83f6-694bc49724f7.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/108e5fc2-7823-42c3-83f6-694bc49724f7.jpg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/adc2bf8e-b37f-4173-9122-4d60a7267536.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/adc2bf8e-b37f-4173-9122-4d60a7267536.jpg</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr"/>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/0efd3afd-d7c6-462e-9c39-7b3a003a9174.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/0efd3afd-d7c6-462e-9c39-7b3a003a9174.jpg</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr"/>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/1bb937b7-6502-4205-8c30-5ac4b4432f76.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/1bb937b7-6502-4205-8c30-5ac4b4432f76.png</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr"/>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/e8ed2803-8d68-4314-8427-b4072ca1dc2f.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/e8ed2803-8d68-4314-8427-b4072ca1dc2f.jpg</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr"/>
@@ -4543,12 +4543,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/b3f5d510-586a-47c7-8d66-ac25cd3a2d1e.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/b3f5d510-586a-47c7-8d66-ac25cd3a2d1e.jpg</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/1f8f208c-fdb6-4185-85fd-4ace5243bfb8.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/1f8f208c-fdb6-4185-85fd-4ace5243bfb8.jpg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>https://gamesdb-images.launchbox.gg/r2_8654f763-7794-4bc0-9768-391ff4e8994e.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/r2_8654f763-7794-4bc0-9768-391ff4e8994e.jpg</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>https://gamesdb-images.launchbox.gg/r2_9285f705-3b23-4428-ae09-61fe70437225.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/r2_9285f705-3b23-4428-ae09-61fe70437225.jpg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/ad0d72d1-3319-4fc0-aa18-e5faf2285b3a.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/ad0d72d1-3319-4fc0-aa18-e5faf2285b3a.jpg</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr"/>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/bcf7f4e8-0a51-4022-aaaf-15af23d3d19e.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/bcf7f4e8-0a51-4022-aaaf-15af23d3d19e.jpg</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/418fccca-633f-442a-831b-744c8c4b7296.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/418fccca-633f-442a-831b-744c8c4b7296.jpg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/59becddc-4e6f-414b-81ca-9725da0d0d65.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/59becddc-4e6f-414b-81ca-9725da0d0d65.jpg</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr"/>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/201c1783-5da6-4884-b4d8-413a8c4d52b6.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/201c1783-5da6-4884-b4d8-413a8c4d52b6.png</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/fec92f07-d703-4e94-bd6a-f42cf8fc9cca.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/fec92f07-d703-4e94-bd6a-f42cf8fc9cca.jpg</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr"/>
@@ -6271,12 +6271,12 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/ec87f17f-3a67-4f2c-bffc-31bc81d7cb4d.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/ec87f17f-3a67-4f2c-bffc-31bc81d7cb4d.jpg</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/9ebc575d-cacc-44cf-adf8-e97942431f57.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/9ebc575d-cacc-44cf-adf8-e97942431f57.jpg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/c74a1751-c246-4260-874b-badbae203bc4.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/c74a1751-c246-4260-874b-badbae203bc4.png</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr"/>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/5eb3d944-5e39-4952-932c-f2379a91bbe2.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/5eb3d944-5e39-4952-932c-f2379a91bbe2.png</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr"/>
@@ -6920,12 +6920,12 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/3a80cfd4-ec8a-4e6b-8ca2-bef7927f88d7.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/3a80cfd4-ec8a-4e6b-8ca2-bef7927f88d7.jpg</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/57279338-9a0a-42c6-b558-0887e31a565d.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/57279338-9a0a-42c6-b558-0887e31a565d.png</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/d8ede60d-d244-46da-9ac7-1ecc040f3d1f.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/d8ede60d-d244-46da-9ac7-1ecc040f3d1f.jpg</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/4b9e713f-1296-4f2d-a8cd-003e13311c61.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/4b9e713f-1296-4f2d-a8cd-003e13311c61.jpg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/6148cffd-abab-4baf-b5ed-0f27bec853f4.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/6148cffd-abab-4baf-b5ed-0f27bec853f4.jpg</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/ef8d05c3-0177-4f01-916c-fbe00b1f91e8.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/ef8d05c3-0177-4f01-916c-fbe00b1f91e8.jpg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/81c8f592-105b-4c1f-b36f-a92cbb76038f.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/81c8f592-105b-4c1f-b36f-a92cbb76038f.jpg</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/7519babc-75f8-4d00-989e-6652cd9de2a4.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/7519babc-75f8-4d00-989e-6652cd9de2a4.jpg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/60e5b98f-3879-4ad9-b236-34da237c1471.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/60e5b98f-3879-4ad9-b236-34da237c1471.jpg</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/03058abb-fe38-4539-9a40-911f86262bbe.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/03058abb-fe38-4539-9a40-911f86262bbe.jpg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8015,12 +8015,12 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/6e2ecabf-a22a-47b5-b9f4-29d6fabd3a7e.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/6e2ecabf-a22a-47b5-b9f4-29d6fabd3a7e.jpg</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/47691f5b-7261-4ef9-85c4-2dbf6346b3f0.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/47691f5b-7261-4ef9-85c4-2dbf6346b3f0.jpg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/b891f245-c57c-427b-ac50-dc54ba7f6c6a.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/b891f245-c57c-427b-ac50-dc54ba7f6c6a.jpg</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/7b4db465-5894-41f4-8439-53c5e795f913.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/7b4db465-5894-41f4-8439-53c5e795f913.jpg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8453,12 +8453,12 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/862ef025-92a7-4b34-a797-c600959ad860.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/862ef025-92a7-4b34-a797-c600959ad860.jpg</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/179ca2a9-262d-4dc6-8b28-baeb458c31e2.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/179ca2a9-262d-4dc6-8b28-baeb458c31e2.jpg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/6e9c60cb-a2ea-48eb-b521-d6c970999e4a.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/6e9c60cb-a2ea-48eb-b521-d6c970999e4a.jpg</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr"/>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/06f1532f-d829-4391-9f75-b86a1061b974.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/06f1532f-d829-4391-9f75-b86a1061b974.jpg</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr"/>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/3cff84c1-1283-4e9d-822e-a815f8dbf3de.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/3cff84c1-1283-4e9d-822e-a815f8dbf3de.jpg</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr"/>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/6a441dac-eeb7-4b42-8790-02d88c2bd718.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/6a441dac-eeb7-4b42-8790-02d88c2bd718.jpg</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr"/>
@@ -9532,12 +9532,12 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/e2519a6a-f94c-4a9a-9ef8-803593c621a6.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/e2519a6a-f94c-4a9a-9ef8-803593c621a6.png</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/65a99349-1929-4999-afe9-6d53522b27bb.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/65a99349-1929-4999-afe9-6d53522b27bb.jpg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/fa6fc183-8d78-4bdd-ba60-2573aa32bda8.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/fa6fc183-8d78-4bdd-ba60-2573aa32bda8.jpg</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/dd43c03c-5800-463a-babb-840b51fbe45e.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/dd43c03c-5800-463a-babb-840b51fbe45e.jpg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/72a61d13-f05a-4727-81ac-1de194ccfc35.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/72a61d13-f05a-4727-81ac-1de194ccfc35.jpg</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr"/>
@@ -10185,12 +10185,12 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/d3bb536b-9aca-423b-865e-f07261592f24.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/d3bb536b-9aca-423b-865e-f07261592f24.jpg</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/ce0bab2e-1a53-43fc-b7a2-eb5168ce23fa.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/ce0bab2e-1a53-43fc-b7a2-eb5168ce23fa.jpg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/4366934a-1ad4-4ad3-87ea-601065ba353f.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/4366934a-1ad4-4ad3-87ea-601065ba353f.jpg</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr"/>
@@ -10619,12 +10619,12 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/0d5247fd-e733-452c-8668-5b05d3efeefa.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/0d5247fd-e733-452c-8668-5b05d3efeefa.jpg</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/3033c93c-a841-432e-a828-a30e6d402a04.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/3033c93c-a841-432e-a828-a30e6d402a04.jpg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/627f25c2-fd9d-467a-b4b3-31f13f1ee4bf.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/627f25c2-fd9d-467a-b4b3-31f13f1ee4bf.png</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr"/>
@@ -11053,12 +11053,12 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/6964836f-a6af-4062-af87-858570190259.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/6964836f-a6af-4062-af87-858570190259.jpg</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/2005f399-e2b3-4f5e-9173-08b255191559.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/2005f399-e2b3-4f5e-9173-08b255191559.jpg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/0f32025a-b913-4b18-8b76-fef2ed10df8f.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/0f32025a-b913-4b18-8b76-fef2ed10df8f.png</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/f8c23f75-2be1-4f5a-9247-f88920168e32.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/f8c23f75-2be1-4f5a-9247-f88920168e32.jpg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/864780ed-3b46-455f-a9dd-c1603eee8cdb.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/864780ed-3b46-455f-a9dd-c1603eee8cdb.png</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/6e71d7fd-aff7-4005-81b3-daee20a1d4e1.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/6e71d7fd-aff7-4005-81b3-daee20a1d4e1.jpg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11710,12 +11710,12 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/d3d4b2f2-1214-458f-9301-6df08dad5503.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/d3d4b2f2-1214-458f-9301-6df08dad5503.jpg</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/ce61a7d8-8c8e-4806-99f5-b39b435692f5.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/ce61a7d8-8c8e-4806-99f5-b39b435692f5.jpg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/7b450117-5e43-4959-81c2-7e478dcdae62.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/7b450117-5e43-4959-81c2-7e478dcdae62.jpg</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/d9a07ec4-92bc-406e-8c96-1d5016ffbc1f.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/d9a07ec4-92bc-406e-8c96-1d5016ffbc1f.jpg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/a617fc5e-9863-4446-909d-56256372a6a8.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/a617fc5e-9863-4446-909d-56256372a6a8.png</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr"/>
@@ -12363,12 +12363,12 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/5f3108d6-3aa2-4d8c-a87d-60fd1bd835f8.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/5f3108d6-3aa2-4d8c-a87d-60fd1bd835f8.jpg</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/bf6825e1-4c11-4f3f-a6e0-a15151a633e2.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/bf6825e1-4c11-4f3f-a6e0-a15151a633e2.jpg</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/5728e065-4961-449c-bc65-2dd9e7254fa9.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/5728e065-4961-449c-bc65-2dd9e7254fa9.jpg</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr"/>
@@ -12797,7 +12797,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/14969787-da13-431c-8737-f5f586c201c4.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/14969787-da13-431c-8737-f5f586c201c4.jpg</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr"/>
@@ -13012,7 +13012,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/ecc28332-ca06-4192-99b6-335dbd71a7d4.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/ecc28332-ca06-4192-99b6-335dbd71a7d4.jpg</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr"/>
@@ -13227,12 +13227,12 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/97aa4da1-772e-4952-b6a0-860ade120b89.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/97aa4da1-772e-4952-b6a0-860ade120b89.jpg</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/0bb3315e-4940-4260-857d-95295596b2a5.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/0bb3315e-4940-4260-857d-95295596b2a5.jpg</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/00115369-b999-4fae-a27a-bb0e6b691843.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/00115369-b999-4fae-a27a-bb0e6b691843.jpg</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr"/>
@@ -13661,12 +13661,12 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/7ab9eb0f-afc6-4224-a772-e9c042c740db.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/7ab9eb0f-afc6-4224-a772-e9c042c740db.jpg</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/cc431602-8bad-4f3c-998d-a04857ca023e.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/cc431602-8bad-4f3c-998d-a04857ca023e.jpg</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13880,12 +13880,12 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/351d4c37-b167-4567-9abe-ae57800a233a.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/351d4c37-b167-4567-9abe-ae57800a233a.jpg</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/d8ffae33-e1b8-4e12-b6ad-a04f1481a2ca.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/d8ffae33-e1b8-4e12-b6ad-a04f1481a2ca.jpg</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -14099,12 +14099,12 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/ecc97767-ff98-4111-833d-9e5588fee00b.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/ecc97767-ff98-4111-833d-9e5588fee00b.jpg</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/d646e91d-9e0c-4bd3-8a10-e15a7d7dab95.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/d646e91d-9e0c-4bd3-8a10-e15a7d7dab95.jpg</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/60126fb9-9e7f-40e3-81dd-10c05e225e21.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/60126fb9-9e7f-40e3-81dd-10c05e225e21.jpg</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/f7a6e8a7-1cd2-405e-bc21-6a8c9acf863c.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/f7a6e8a7-1cd2-405e-bc21-6a8c9acf863c.png</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14537,12 +14537,12 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/2f5e8f0f-645d-4a8e-8736-4f15090ce6bb.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/2f5e8f0f-645d-4a8e-8736-4f15090ce6bb.jpg</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/684d0036-447b-40c0-b9b1-000886b7533b.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/684d0036-447b-40c0-b9b1-000886b7533b.jpg</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -14756,12 +14756,12 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/ccf0c30e-1f5e-46fe-afee-42bd7e651796.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/ccf0c30e-1f5e-46fe-afee-42bd7e651796.jpg</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/1f0039bb-3c00-40f9-9e33-ba070369b7ca.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/1f0039bb-3c00-40f9-9e33-ba070369b7ca.jpg</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14975,12 +14975,12 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/a726a6dc-98bf-4ab9-89d5-b9c095d75f3b.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/a726a6dc-98bf-4ab9-89d5-b9c095d75f3b.jpg</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/48563dfc-bbf3-47cd-bc8c-81ab2692536f.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/48563dfc-bbf3-47cd-bc8c-81ab2692536f.jpg</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/3735e08c-9ff5-4f4f-bb48-5a763e8aa92d.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/3735e08c-9ff5-4f4f-bb48-5a763e8aa92d.jpg</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/257395e2-b4b4-45d7-b1e4-2cdb42867db2.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/257395e2-b4b4-45d7-b1e4-2cdb42867db2.jpg</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -15413,12 +15413,12 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/8738eba1-ed19-4784-8268-f0dfe69b7a41.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/8738eba1-ed19-4784-8268-f0dfe69b7a41.jpg</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/780117a7-d7d7-42d0-860c-b3f5fe4d5d9a.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/780117a7-d7d7-42d0-860c-b3f5fe4d5d9a.jpg</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15632,12 +15632,12 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/af9313b6-0856-4195-b4b2-7d7c9ee07475.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/af9313b6-0856-4195-b4b2-7d7c9ee07475.jpg</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/c47b57fc-8029-419f-85f9-f26aaf4fdf6b.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/c47b57fc-8029-419f-85f9-f26aaf4fdf6b.jpg</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15851,12 +15851,12 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/2a6194ee-bea2-47f9-94ec-e2f4bc5ed6f7.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/2a6194ee-bea2-47f9-94ec-e2f4bc5ed6f7.jpg</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/4630405e-b5e9-482a-b6bb-d78c3552ef60.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/4630405e-b5e9-482a-b6bb-d78c3552ef60.jpg</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -16070,12 +16070,12 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/6e1e4d3a-83b9-40dc-8552-14a43fd00efb.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/6e1e4d3a-83b9-40dc-8552-14a43fd00efb.jpg</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/8089cb3a-532f-4090-b045-3a111491fd1d.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/8089cb3a-532f-4090-b045-3a111491fd1d.jpg</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16289,7 +16289,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/d7021562-3e9c-42d7-89e4-512d5e2e5476.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/d7021562-3e9c-42d7-89e4-512d5e2e5476.jpg</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr"/>
@@ -16504,12 +16504,12 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/22c14050-3eef-4932-943b-afdda005a3e4.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/22c14050-3eef-4932-943b-afdda005a3e4.jpg</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/dea95cd6-61bd-4109-ae1e-516e8b6d2873.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/dea95cd6-61bd-4109-ae1e-516e8b6d2873.jpg</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -16723,12 +16723,12 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>https://gamesdb-images.launchbox.gg/r2_f673f947-c6fc-41f4-978a-2ee373c28398.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/r2_f673f947-c6fc-41f4-978a-2ee373c28398.jpg</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>https://gamesdb-images.launchbox.gg/r2_26dabfdf-6c6e-4888-8468-4e6a5bcc5894.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/r2_26dabfdf-6c6e-4888-8468-4e6a5bcc5894.jpg</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16942,12 +16942,12 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/6810aab9-bd2d-4fec-bb3a-ff606513a32b.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/6810aab9-bd2d-4fec-bb3a-ff606513a32b.jpg</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/f0819219-6010-4061-a254-3d02c48e2c93.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/f0819219-6010-4061-a254-3d02c48e2c93.jpg</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17161,7 +17161,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/fded9f55-1af5-472e-a647-500c4d38d0fb.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/fded9f55-1af5-472e-a647-500c4d38d0fb.png</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr"/>
@@ -17376,7 +17376,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/f3fb33c2-7c49-42c4-a099-cc09dc45c26e.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/f3fb33c2-7c49-42c4-a099-cc09dc45c26e.jpg</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr"/>
@@ -17802,12 +17802,12 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/08c71f68-866c-42d9-8df0-15539bbd1e85.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/08c71f68-866c-42d9-8df0-15539bbd1e85.jpg</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/e3f872a1-a93d-48ef-8337-57431be28c6f.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/e3f872a1-a93d-48ef-8337-57431be28c6f.jpg</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -18021,12 +18021,12 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/b9383c77-eb1e-4d67-b3d6-2e68125899a6.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/b9383c77-eb1e-4d67-b3d6-2e68125899a6.jpg</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/8c93cbc9-8623-42c0-8b20-f5ab8e404363.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/8c93cbc9-8623-42c0-8b20-f5ab8e404363.jpg</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18240,7 +18240,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/926f54f8-045b-4115-b2a3-7354cde06f62.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/926f54f8-045b-4115-b2a3-7354cde06f62.png</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr"/>
@@ -18455,12 +18455,12 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/e220a74f-0efa-40c2-9cdb-b27495f279fe.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/e220a74f-0efa-40c2-9cdb-b27495f279fe.png</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/a2c7d7a9-9216-4568-becb-c8cf46155f1e.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/a2c7d7a9-9216-4568-becb-c8cf46155f1e.jpg</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -18674,12 +18674,12 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/39dea5f5-fbda-45e5-b401-3ba29d8d7800.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/39dea5f5-fbda-45e5-b401-3ba29d8d7800.jpg</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/6e485788-1e83-425f-b4f4-76891125f43b.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/6e485788-1e83-425f-b4f4-76891125f43b.jpg</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18893,12 +18893,12 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/e47faf12-7547-4704-b56f-233d8608f4a7.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/e47faf12-7547-4704-b56f-233d8608f4a7.jpg</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/113ce600-33cd-46ba-b24a-29d399b7e799.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/113ce600-33cd-46ba-b24a-29d399b7e799.jpg</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19112,12 +19112,12 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/e8e34d20-c9d1-486b-b1ed-231130f86e8a.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/e8e34d20-c9d1-486b-b1ed-231130f86e8a.jpg</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/33525654-5cb6-4046-b4a1-6d13ab40b6b5.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/33525654-5cb6-4046-b4a1-6d13ab40b6b5.jpg</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -19331,12 +19331,12 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/452bb923-0915-4456-81a1-72ac66fd7b23.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/452bb923-0915-4456-81a1-72ac66fd7b23.jpg</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/34f0f81b-0e66-4f73-a8db-7758d800eaa3.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/34f0f81b-0e66-4f73-a8db-7758d800eaa3.jpg</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19550,7 +19550,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/fee8e619-bbf8-41f7-b53e-5308bfebb719.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/fee8e619-bbf8-41f7-b53e-5308bfebb719.jpg</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr"/>
@@ -19765,12 +19765,12 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/0b53dbdc-230d-41fb-b391-db28b5001603.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/0b53dbdc-230d-41fb-b391-db28b5001603.jpg</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/6b73b8c4-4a08-41d3-8031-f7d091fcac5a.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/6b73b8c4-4a08-41d3-8031-f7d091fcac5a.jpg</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -19984,12 +19984,12 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/2f4409b2-6c02-4839-a7ae-31e14fce1bde.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/2f4409b2-6c02-4839-a7ae-31e14fce1bde.jpg</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/aec4beb9-65bc-43f4-ad2c-23461bfb0c37.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/aec4beb9-65bc-43f4-ad2c-23461bfb0c37.jpg</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20203,7 +20203,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/4b9356e3-0341-4ae6-b4c5-2b7a9898d22a.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/4b9356e3-0341-4ae6-b4c5-2b7a9898d22a.png</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr"/>
@@ -20418,12 +20418,12 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/277a7f3b-2679-4b1e-829e-68573e579617.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/277a7f3b-2679-4b1e-829e-68573e579617.jpg</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/a09bda66-be33-4076-ae6f-3e655942cf45.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/a09bda66-be33-4076-ae6f-3e655942cf45.jpg</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -20637,12 +20637,12 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/64440448-c681-486f-93c6-9d013180cbf7.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/64440448-c681-486f-93c6-9d013180cbf7.jpg</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/765dfb43-0956-405a-b2f6-b26f0a132931.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/765dfb43-0956-405a-b2f6-b26f0a132931.jpg</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20856,12 +20856,12 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/54c647da-92af-4f6e-b3eb-2776175464c3.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/54c647da-92af-4f6e-b3eb-2776175464c3.jpg</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/00dc5230-d100-4520-9335-53d05b705bce.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/00dc5230-d100-4520-9335-53d05b705bce.jpg</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -21075,12 +21075,12 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/50caa83f-6223-4cdb-b752-26b4d8113eb4.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/50caa83f-6223-4cdb-b752-26b4d8113eb4.jpg</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/19e61927-fca1-439f-8caf-0110dea33078.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/19e61927-fca1-439f-8caf-0110dea33078.jpg</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -21294,12 +21294,12 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/d642cc66-3aa1-46ad-8230-1176188afac9.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/d642cc66-3aa1-46ad-8230-1176188afac9.jpg</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/06feb386-280f-4eea-a159-de1a4239a158.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/06feb386-280f-4eea-a159-de1a4239a158.jpg</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21513,12 +21513,12 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/1c426727-0362-4158-a590-1e2e2a52d6a1.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/1c426727-0362-4158-a590-1e2e2a52d6a1.jpg</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/9534bbcf-90f8-4c8f-9673-7cdf57411bb0.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/9534bbcf-90f8-4c8f-9673-7cdf57411bb0.jpg</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21732,12 +21732,12 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/2ff7fdbf-212b-4677-a04d-3e58b83ffa33.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/2ff7fdbf-212b-4677-a04d-3e58b83ffa33.jpg</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/d841f87e-45b2-4033-903d-ba89b12a18f4.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/d841f87e-45b2-4033-903d-ba89b12a18f4.jpg</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -21951,12 +21951,12 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/b3424b2d-b7a6-4f85-acb3-18fd4c3ac68b.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/b3424b2d-b7a6-4f85-acb3-18fd4c3ac68b.jpg</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/50d802a9-bf8b-43c3-bd5a-47a31a49a9f7.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/50d802a9-bf8b-43c3-bd5a-47a31a49a9f7.jpg</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -22170,12 +22170,12 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/aa337abb-1482-4359-8c40-8dc25a00dbc5.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/aa337abb-1482-4359-8c40-8dc25a00dbc5.jpg</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/c2317b0e-f60f-4eab-9483-4e6259f5442e.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/c2317b0e-f60f-4eab-9483-4e6259f5442e.jpg</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22389,12 +22389,12 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/7b464f55-d193-425a-bcf5-d849adb70503.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/7b464f55-d193-425a-bcf5-d849adb70503.jpg</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/4b093bf9-097d-417b-962f-83dacc43567b.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/4b093bf9-097d-417b-962f-83dacc43567b.jpg</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/b68ac0af-5714-40c5-9a76-4f3d75af8033.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/b68ac0af-5714-40c5-9a76-4f3d75af8033.jpg</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/cebb69fd-d2ec-4040-ba37-e45c94553acf.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/cebb69fd-d2ec-4040-ba37-e45c94553acf.jpg</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/e5c465c2-4f34-4bea-9022-6e9620239efb.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/e5c465c2-4f34-4bea-9022-6e9620239efb.jpg</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/c45fff34-feaf-478a-8330-e32e960c9e54.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/c45fff34-feaf-478a-8330-e32e960c9e54.jpg</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -23046,12 +23046,12 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/e4d31169-3e74-4ff3-b379-ccf4d07da71d.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/e4d31169-3e74-4ff3-b379-ccf4d07da71d.jpg</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/c82cc80e-27f2-4ced-aad1-c9af7c1a6842.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/c82cc80e-27f2-4ced-aad1-c9af7c1a6842.jpg</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -23265,12 +23265,12 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/fdc82a8a-1e70-41d5-91f8-91f78d43e204.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/fdc82a8a-1e70-41d5-91f8-91f78d43e204.jpg</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/38c9c257-b1ef-4a98-a810-cb7f04c9ec55.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/38c9c257-b1ef-4a98-a810-cb7f04c9ec55.jpg</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/0121711b-7ffc-4b87-959d-df5ea0709b1e.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/0121711b-7ffc-4b87-959d-df5ea0709b1e.jpg</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/b813149e-5b02-4f41-bc03-7a4e537f0aaf.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/b813149e-5b02-4f41-bc03-7a4e537f0aaf.jpg</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23703,12 +23703,12 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/2a233c3c-9e79-4209-8452-f32c3381800c.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/2a233c3c-9e79-4209-8452-f32c3381800c.jpg</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/f8b4e8b0-7716-4431-ba86-07cc08f8f116.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/f8b4e8b0-7716-4431-ba86-07cc08f8f116.jpg</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -23922,12 +23922,12 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/07acfb71-f91f-4916-bd17-4c60fffcc20e.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/07acfb71-f91f-4916-bd17-4c60fffcc20e.jpg</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/2cd18d8e-6417-419a-96b9-9dc2c9e04a68.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/2cd18d8e-6417-419a-96b9-9dc2c9e04a68.jpg</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -24141,7 +24141,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/a14f85ff-8469-4d54-a687-e5de8eac08fc.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/a14f85ff-8469-4d54-a687-e5de8eac08fc.jpg</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr"/>
@@ -24356,7 +24356,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/f4c1b249-8f77-4816-9cf4-c2d98ec8b422.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/f4c1b249-8f77-4816-9cf4-c2d98ec8b422.jpg</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr"/>
@@ -24571,7 +24571,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/8e8ffa12-06ac-465f-9e01-8c03d76e7e3c.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/8e8ffa12-06ac-465f-9e01-8c03d76e7e3c.jpg</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr"/>
@@ -24786,7 +24786,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/df447208-c066-4795-b328-e1a2d1672ddf.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/df447208-c066-4795-b328-e1a2d1672ddf.jpg</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr"/>
@@ -25001,12 +25001,12 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/1ba5ca41-245a-41cf-b706-a89a1ce8d63f.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/1ba5ca41-245a-41cf-b706-a89a1ce8d63f.jpg</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/d906551d-4af5-402b-9cc8-3d13ede6777c.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/d906551d-4af5-402b-9cc8-3d13ede6777c.jpg</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -25220,12 +25220,12 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/0e22f16d-cf0f-46d4-963f-354f0b251d5d.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/0e22f16d-cf0f-46d4-963f-354f0b251d5d.jpg</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/f3598c0e-5181-4950-bcb3-f490063c0432.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/f3598c0e-5181-4950-bcb3-f490063c0432.jpg</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -25439,12 +25439,12 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/135f9c65-c4ca-40ce-8977-1c71b8d3dbda.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/135f9c65-c4ca-40ce-8977-1c71b8d3dbda.jpg</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/fa910a05-4094-44e2-a51f-a90abb795069.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/fa910a05-4094-44e2-a51f-a90abb795069.jpg</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25658,12 +25658,12 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/83ee826e-1b58-4f00-bc40-de2996623b88.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/83ee826e-1b58-4f00-bc40-de2996623b88.jpg</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/9ac63cd9-a64c-4e1b-bac4-c203721275d1.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/9ac63cd9-a64c-4e1b-bac4-c203721275d1.png</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -25877,12 +25877,12 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/81fc5962-ce73-41aa-b194-7f8205f3fd5b.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/81fc5962-ce73-41aa-b194-7f8205f3fd5b.jpg</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/78360653-4c90-4e71-8bac-f8546b1a0396.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/78360653-4c90-4e71-8bac-f8546b1a0396.png</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -26096,12 +26096,12 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/a94bdd9b-644f-4e53-8695-48be8ef5498d.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/a94bdd9b-644f-4e53-8695-48be8ef5498d.jpg</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/df3ddfac-b774-4c0d-9f01-4f86ba07124f.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/df3ddfac-b774-4c0d-9f01-4f86ba07124f.jpg</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -26315,12 +26315,12 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/a159692a-373d-4f50-84c3-9392cd2745f4.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/a159692a-373d-4f50-84c3-9392cd2745f4.jpg</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/d27be10d-bfbe-4da9-a456-353269ab43b0.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/d27be10d-bfbe-4da9-a456-353269ab43b0.jpg</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/2d00bcf3-f3d7-46f3-8a6c-c94f0d804f3c.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/2d00bcf3-f3d7-46f3-8a6c-c94f0d804f3c.jpg</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr"/>
@@ -26749,7 +26749,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/95339a61-19ae-4ca6-aa8e-d26e945a5274.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/95339a61-19ae-4ca6-aa8e-d26e945a5274.jpg</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr"/>
@@ -26964,12 +26964,12 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/cffe7614-fdba-4d79-8782-f0fa79a998b9.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/cffe7614-fdba-4d79-8782-f0fa79a998b9.jpg</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/06bc538c-9217-4f0e-b6bc-f3fef8dfdca6.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/06bc538c-9217-4f0e-b6bc-f3fef8dfdca6.jpg</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -27183,12 +27183,12 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/77109dd0-7bda-4665-ac48-95fbfca9eaed.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/77109dd0-7bda-4665-ac48-95fbfca9eaed.jpg</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/a26ea52e-2cf8-4c91-959f-b2068e372013.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/a26ea52e-2cf8-4c91-959f-b2068e372013.jpg</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -27402,12 +27402,12 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/ae5c73b6-87d4-4917-9815-976df7556c55.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/ae5c73b6-87d4-4917-9815-976df7556c55.jpg</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/c11e5992-2f70-434e-8406-6c8753fe0af1.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/c11e5992-2f70-434e-8406-6c8753fe0af1.jpg</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27621,12 +27621,12 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/329264aa-6487-4b1a-ac61-c8a8ec4bb512.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/329264aa-6487-4b1a-ac61-c8a8ec4bb512.jpg</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/780f6ab3-ef53-4cc9-b346-5ff75d49be35.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/780f6ab3-ef53-4cc9-b346-5ff75d49be35.jpg</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -27840,12 +27840,12 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/3b0fc2f7-42fc-4a4e-8498-99893577233e.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/3b0fc2f7-42fc-4a4e-8498-99893577233e.jpg</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/5c09a288-e5a8-4be2-88c8-9ef667660b18.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/5c09a288-e5a8-4be2-88c8-9ef667660b18.jpg</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -28059,12 +28059,12 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/8aa5f09c-84c2-463b-9489-43e707619e9d.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/8aa5f09c-84c2-463b-9489-43e707619e9d.jpg</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/bc0d4105-241a-4238-99f8-bb09c3b2b85b.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/bc0d4105-241a-4238-99f8-bb09c3b2b85b.jpg</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -28278,12 +28278,12 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/f9b8b096-53c5-4b29-a6aa-8e019adc5bf0.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/f9b8b096-53c5-4b29-a6aa-8e019adc5bf0.jpg</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/753fbdba-9557-4e6a-b067-fd6acaf2ab8d.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/753fbdba-9557-4e6a-b067-fd6acaf2ab8d.jpg</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/b84c7752-25d2-4f0c-8a12-e4a66a4a3c2c.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/b84c7752-25d2-4f0c-8a12-e4a66a4a3c2c.jpg</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr"/>
@@ -28712,12 +28712,12 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/59b92211-e167-4332-bb2b-af73deffa91e.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/59b92211-e167-4332-bb2b-af73deffa91e.jpg</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/443b630c-7596-488d-9712-b5b6f2758bed.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/443b630c-7596-488d-9712-b5b6f2758bed.jpg</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28931,12 +28931,12 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/8edb1afd-228a-40b9-b582-c196037a9c85.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/8edb1afd-228a-40b9-b582-c196037a9c85.jpg</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/9b2e7edd-0c78-4946-866c-a86fc0c23ef7.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/9b2e7edd-0c78-4946-866c-a86fc0c23ef7.jpg</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -29150,12 +29150,12 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/be157676-8227-4455-81d4-f6e023992c8b.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/be157676-8227-4455-81d4-f6e023992c8b.jpg</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/7f2962d2-17bd-4f88-9bd9-1dd05fbcc470.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/7f2962d2-17bd-4f88-9bd9-1dd05fbcc470.jpg</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -29369,12 +29369,12 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/09be0ea7-c232-4391-b48c-4653b633b427.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/09be0ea7-c232-4391-b48c-4653b633b427.jpg</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/ebf19f56-a243-4bae-8e87-24cdeba9d767.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/ebf19f56-a243-4bae-8e87-24cdeba9d767.jpg</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29588,12 +29588,12 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/ab1a4c23-df55-47d5-9a09-3af22835683a.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/ab1a4c23-df55-47d5-9a09-3af22835683a.jpg</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/05947a23-6cb9-4a3f-8282-5a7c2a474bcf.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/05947a23-6cb9-4a3f-8282-5a7c2a474bcf.png</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -29807,12 +29807,12 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/b17eefce-1f26-46c0-8f1d-25e974bfc5a6.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/b17eefce-1f26-46c0-8f1d-25e974bfc5a6.jpg</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/745809b9-74cc-4150-a25e-0be28adf2e11.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/745809b9-74cc-4150-a25e-0be28adf2e11.jpg</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/fbad7ca7-277b-4d36-992f-7b7e30e6a403.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/fbad7ca7-277b-4d36-992f-7b7e30e6a403.jpg</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/0859e5d7-aed7-4bd0-a2d4-e7d3547a1b81.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/0859e5d7-aed7-4bd0-a2d4-e7d3547a1b81.jpg</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -30245,12 +30245,12 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/71343a42-76e3-4fa3-aa10-68f3664ca3ec.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/71343a42-76e3-4fa3-aa10-68f3664ca3ec.jpg</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/d856bcf2-98ab-4491-813c-f0f5bc128606.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/d856bcf2-98ab-4491-813c-f0f5bc128606.jpg</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -30464,12 +30464,12 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/4001be79-73b1-492e-ac12-d048cf2e2479.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/4001be79-73b1-492e-ac12-d048cf2e2479.jpg</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/f8c191ba-e022-40c1-8d33-39637a7bef15.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/f8c191ba-e022-40c1-8d33-39637a7bef15.jpg</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/6758ce4f-4237-4cd0-8d8c-1d2692abe90d.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/6758ce4f-4237-4cd0-8d8c-1d2692abe90d.jpg</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr"/>
@@ -30898,12 +30898,12 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/13e8968e-2ade-48db-84eb-75aabfb0b401.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/13e8968e-2ade-48db-84eb-75aabfb0b401.jpg</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/28ba3888-d73b-4c12-b1d5-9a9bc04e18a8.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/28ba3888-d73b-4c12-b1d5-9a9bc04e18a8.jpg</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -31117,7 +31117,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>https://images.launchbox-app.com/44d711df-cb04-465d-ad74-95d54afdf269.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/44d711df-cb04-465d-ad74-95d54afdf269.jpg</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr"/>

--- a/data/RetroVault_GS_Games_全量匯入檔.xlsx
+++ b/data/RetroVault_GS_Games_全量匯入檔.xlsx
@@ -31327,7 +31327,7 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Heiwa%20Parlor%21%20Mini%208%20-%20Pachinko%20Jikki%20Simulation%20Game%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Parlor%21%20Parlor%21%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
@@ -31338,7 +31338,7 @@
       <c r="AJ142" t="inlineStr"/>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Heiwa%20Parlor%21%20Mini%208%20-%20Pachinko%20Jikki%20Simulation%20Game%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Parlor%21%20Parlor%21%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr"/>
@@ -32179,7 +32179,7 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Masters%20-%20Harukanaru%20Augusta%202%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/New%203D%20Golf%20Simulation%20-%20Harukanaru%20Augusta%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
@@ -32190,7 +32190,7 @@
       <c r="AJ146" t="inlineStr"/>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Masters%20-%20Harukanaru%20Augusta%202%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/New%203D%20Golf%20Simulation%20-%20Harukanaru%20Augusta%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr"/>
@@ -36439,7 +36439,7 @@
       </c>
       <c r="AH166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Nobunaga%20no%20Yabou%20-%20Haouden%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Nobunaga%20no%20Yabou%20-%20Haouden%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI166" t="inlineStr">
@@ -36450,7 +36450,7 @@
       <c r="AJ166" t="inlineStr"/>
       <c r="AK166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Nobunaga%20no%20Yabou%20-%20Haouden%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Nobunaga%20no%20Yabou%20-%20Haouden%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL166" t="inlineStr"/>
@@ -36654,7 +36654,7 @@
       </c>
       <c r="AH167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Super%20Nobunaga%20no%20Yabou%20-%20Bushou%20Fuuunroku%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Super%20Nobunaga%20no%20Yabou%20-%20Bushou%20Fuuunroku%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI167" t="inlineStr">
@@ -36665,7 +36665,7 @@
       <c r="AJ167" t="inlineStr"/>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Super%20Nobunaga%20no%20Yabou%20-%20Bushou%20Fuuunroku%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Super%20Nobunaga%20no%20Yabou%20-%20Bushou%20Fuuunroku%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL167" t="inlineStr"/>
@@ -39226,7 +39226,7 @@
       </c>
       <c r="AH179" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Tactics%20Ogre%20-%20Let%20Us%20Cling%20Together%20%28Japan%29%20%28Rev%201%29%20%28Virtual%20Console%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Tactics%20Ogre%20-%20Let%20Us%20Cling%20Together%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI179" t="inlineStr">
@@ -39237,7 +39237,7 @@
       <c r="AJ179" t="inlineStr"/>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Tactics%20Ogre%20-%20Let%20Us%20Cling%20Together%20%28Japan%29%20%28Rev%201%29%20%28Virtual%20Console%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Tactics%20Ogre%20-%20Let%20Us%20Cling%20Together%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL179" t="inlineStr"/>
@@ -39441,7 +39441,7 @@
       </c>
       <c r="AH180" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Densetsu%20no%20Ogre%20Battle%20-%20The%20March%20of%20the%20Black%20Queen%20%28Japan%29%20%28NP%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Densetsu%20no%20Ogre%20Battle%20-%20The%20March%20of%20the%20Black%20Queen%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI180" t="inlineStr">
@@ -39452,7 +39452,7 @@
       <c r="AJ180" t="inlineStr"/>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Densetsu%20no%20Ogre%20Battle%20-%20The%20March%20of%20the%20Black%20Queen%20%28Japan%29%20%28NP%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Densetsu%20no%20Ogre%20Battle%20-%20The%20March%20of%20the%20Black%20Queen%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL180" t="inlineStr"/>
@@ -39656,7 +39656,7 @@
       </c>
       <c r="AH181" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Liberty%20or%20Death%20%28USA%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Dokuritsu%20Sensou%20-%20Liberty%20or%20Death%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI181" t="inlineStr">
@@ -39671,7 +39671,7 @@
       </c>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Liberty%20or%20Death%20%28USA%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Dokuritsu%20Sensou%20-%20Liberty%20or%20Death%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL181" t="inlineStr"/>
@@ -39875,7 +39875,7 @@
       </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Sangokushi%20Eiketsuden%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Super%20Sangokushi%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI182" t="inlineStr">
@@ -39886,7 +39886,7 @@
       <c r="AJ182" t="inlineStr"/>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Sangokushi%20Eiketsuden%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Super%20Sangokushi%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL182" t="inlineStr"/>
@@ -40301,7 +40301,7 @@
       </c>
       <c r="AH184" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Seiken%20Densetsu%203%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Sangokushi%20III%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI184" t="inlineStr">
@@ -40316,7 +40316,7 @@
       </c>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Seiken%20Densetsu%203%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Sangokushi%20III%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL184" t="inlineStr"/>
@@ -40954,7 +40954,7 @@
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Tokimeki%20Memorial%20-%20Densetsu%20no%20Ki%20no%20Shita%20de%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Tokimeki%20Memorial%20-%20Densetsu%20no%20Ki%20no%20Shita%20de%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI187" t="inlineStr">
@@ -40965,7 +40965,7 @@
       <c r="AJ187" t="inlineStr"/>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Tokimeki%20Memorial%20-%20Densetsu%20no%20Ki%20no%20Shita%20de%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Tokimeki%20Memorial%20-%20Densetsu%20no%20Ki%20no%20Shita%20de%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL187" t="inlineStr"/>
@@ -44621,7 +44621,7 @@
       </c>
       <c r="AH204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Nobunaga%20no%20Yabou%20-%20Tenshouki%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Nobunaga%20no%20Yabou%20-%20Tenshouki%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI204" t="inlineStr">
@@ -44632,7 +44632,7 @@
       <c r="AJ204" t="inlineStr"/>
       <c r="AK204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Nobunaga%20no%20Yabou%20-%20Tenshouki%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Nobunaga%20no%20Yabou%20-%20Tenshouki%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL204" t="inlineStr"/>
@@ -45051,14 +45051,14 @@
       </c>
       <c r="AH206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Super%20Sangokushi%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Super%20Sangokushi%20II%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI206" t="inlineStr"/>
       <c r="AJ206" t="inlineStr"/>
       <c r="AK206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Super%20Sangokushi%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Super%20Sangokushi%20II%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL206" t="inlineStr"/>
@@ -46775,7 +46775,7 @@
       </c>
       <c r="AH214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Dragon%20Quest%20V%20-%20Tenkuu%20no%20Hanayome%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Dragon%20Quest%20I%20_%20II%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI214" t="inlineStr">
@@ -46790,7 +46790,7 @@
       </c>
       <c r="AK214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Dragon%20Quest%20V%20-%20Tenkuu%20no%20Hanayome%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Dragon%20Quest%20I%20_%20II%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL214" t="inlineStr"/>
@@ -47213,7 +47213,7 @@
       </c>
       <c r="AH216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Dragon%20Ball%20Z%20-%20Super%20Butouden%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Dragon%20Ball%20Z%20-%20Super%20Butouden%202%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI216" t="inlineStr">
@@ -47228,7 +47228,7 @@
       </c>
       <c r="AK216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Dragon%20Ball%20Z%20-%20Super%20Butouden%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Dragon%20Ball%20Z%20-%20Super%20Butouden%202%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL216" t="inlineStr"/>
@@ -47651,7 +47651,7 @@
       </c>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Dragon%20Ball%20Z%20-%20Super%20Butouden%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Dragon%20Ball%20Z%20-%20Super%20Butouden%203%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI218" t="inlineStr">
@@ -47666,7 +47666,7 @@
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Dragon%20Ball%20Z%20-%20Super%20Butouden%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Dragon%20Ball%20Z%20-%20Super%20Butouden%203%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL218" t="inlineStr"/>
@@ -47870,7 +47870,7 @@
       </c>
       <c r="AH219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Dragon%20Ball%20Z%20-%20Super%20Butouden%20%28Japan%29%20%28Sample%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Dragon%20Ball%20Z%20-%20Super%20Butouden%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI219" t="inlineStr">
@@ -47885,7 +47885,7 @@
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Dragon%20Ball%20Z%20-%20Super%20Butouden%20%28Japan%29%20%28Sample%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Dragon%20Ball%20Z%20-%20Super%20Butouden%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL219" t="inlineStr"/>
@@ -48089,7 +48089,7 @@
       </c>
       <c r="AH220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Dragon%20Ball%20Z%20-%20Super%20Saiya%20Densetsu%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Dragon%20Ball%20Z%20-%20Super%20Saiya%20Densetsu%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI220" t="inlineStr">
@@ -48100,7 +48100,7 @@
       <c r="AJ220" t="inlineStr"/>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Dragon%20Ball%20Z%20-%20Super%20Saiya%20Densetsu%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Dragon%20Ball%20Z%20-%20Super%20Saiya%20Densetsu%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL220" t="inlineStr"/>
@@ -49172,14 +49172,14 @@
       </c>
       <c r="AH225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/J.League%20Soccer%20-%20Prime%20Goal%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/J.League%20Soccer%20-%20Prime%20Goal%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI225" t="inlineStr"/>
       <c r="AJ225" t="inlineStr"/>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/J.League%20Soccer%20-%20Prime%20Goal%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/J.League%20Soccer%20-%20Prime%20Goal%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL225" t="inlineStr"/>
@@ -49383,14 +49383,14 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/J.League%20Soccer%20-%20Prime%20Goal%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/J.League%20Soccer%20-%20Prime%20Goal%202%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr"/>
       <c r="AJ226" t="inlineStr"/>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/J.League%20Soccer%20-%20Prime%20Goal%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/J.League%20Soccer%20-%20Prime%20Goal%202%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr"/>
@@ -49809,14 +49809,14 @@
       </c>
       <c r="AH228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/J.League%20Soccer%20-%20Prime%20Goal%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/J.League%20Soccer%20-%20Prime%20Goal%203%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI228" t="inlineStr"/>
       <c r="AJ228" t="inlineStr"/>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/J.League%20Soccer%20-%20Prime%20Goal%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/J.League%20Soccer%20-%20Prime%20Goal%203%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr"/>
@@ -50231,7 +50231,7 @@
       </c>
       <c r="AH230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Yu%20Yu%20Hakusho%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Yu%20Yu%20Hakusho%20-%20Tokubetsu%20Hen%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI230" t="inlineStr">
@@ -50246,7 +50246,7 @@
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Yu%20Yu%20Hakusho%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Yu%20Yu%20Hakusho%20-%20Tokubetsu%20Hen%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL230" t="inlineStr"/>
@@ -50669,7 +50669,7 @@
       </c>
       <c r="AH232" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Yu%20Yu%20Hakusho%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Yu%20Yu%20Hakusho%202%20-%20Kakutou%20no%20Shou%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI232" t="inlineStr">
@@ -50684,7 +50684,7 @@
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Yu%20Yu%20Hakusho%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Yu%20Yu%20Hakusho%202%20-%20Kakutou%20no%20Shou%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL232" t="inlineStr"/>
@@ -50888,7 +50888,7 @@
       </c>
       <c r="AH233" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Yu%20Yu%20Hakusho%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Yu%20Yu%20Hakusho%20Final%20-%20Makai%20Saikyou%20Retsuden%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI233" t="inlineStr">
@@ -50903,7 +50903,7 @@
       </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Yu%20Yu%20Hakusho%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Yu%20Yu%20Hakusho%20Final%20-%20Makai%20Saikyou%20Retsuden%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL233" t="inlineStr"/>
@@ -52409,7 +52409,7 @@
       </c>
       <c r="AH240" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Garou%20Densetsu%20-%20Shukumei%20no%20Tatakai%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Garou%20Densetsu%20-%20Shukumei%20no%20Tatakai%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI240" t="inlineStr">
@@ -52424,7 +52424,7 @@
       </c>
       <c r="AK240" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Garou%20Densetsu%20-%20Shukumei%20no%20Tatakai%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Garou%20Densetsu%20-%20Shukumei%20no%20Tatakai%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL240" t="inlineStr"/>
@@ -52843,7 +52843,7 @@
       </c>
       <c r="AH242" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Garou%20Densetsu%202%20-%20Aratanaru%20Tatakai%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Garou%20Densetsu%202%20-%20Aratanaru%20Tatakai%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI242" t="inlineStr">
@@ -52858,7 +52858,7 @@
       </c>
       <c r="AK242" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Garou%20Densetsu%202%20-%20Aratanaru%20Tatakai%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Garou%20Densetsu%202%20-%20Aratanaru%20Tatakai%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL242" t="inlineStr"/>
@@ -53062,7 +53062,7 @@
       </c>
       <c r="AH243" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Fire%20Emblem%20-%20Monshou%20no%20Nazo%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Fire%20Emblem%20-%20Monshou%20no%20Nazo%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI243" t="inlineStr">
@@ -53073,7 +53073,7 @@
       <c r="AJ243" t="inlineStr"/>
       <c r="AK243" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Fire%20Emblem%20-%20Monshou%20no%20Nazo%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Fire%20Emblem%20-%20Monshou%20no%20Nazo%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL243" t="inlineStr"/>
@@ -54587,7 +54587,7 @@
       </c>
       <c r="AH250" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Front%20Mission%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Front%20Mission%20Series%20-%20Gun%20Hazard%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI250" t="inlineStr">
@@ -54598,7 +54598,7 @@
       <c r="AJ250" t="inlineStr"/>
       <c r="AK250" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Front%20Mission%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Front%20Mission%20Series%20-%20Gun%20Hazard%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL250" t="inlineStr"/>
@@ -54802,7 +54802,7 @@
       </c>
       <c r="AH251" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Feda%20-%20The%20Emblem%20of%20Justice%20%28Japan%29%20%28Beta%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Feda%20-%20The%20Emblem%20of%20Justice%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI251" t="inlineStr">
@@ -54817,7 +54817,7 @@
       </c>
       <c r="AK251" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Feda%20-%20The%20Emblem%20of%20Justice%20%28Japan%29%20%28Beta%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Feda%20-%20The%20Emblem%20of%20Justice%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL251" t="inlineStr"/>
@@ -56753,14 +56753,14 @@
       </c>
       <c r="AH260" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Super%20Donkey%20Kong%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Super%20Donkey%20Kong%202%20-%20Dixie%20_%20Diddy%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI260" t="inlineStr"/>
       <c r="AJ260" t="inlineStr"/>
       <c r="AK260" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Super%20Donkey%20Kong%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Super%20Donkey%20Kong%202%20-%20Dixie%20_%20Diddy%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL260" t="inlineStr"/>
@@ -57398,14 +57398,14 @@
       </c>
       <c r="AH263" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Super%20Donkey%20Kong%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Super%20Donkey%20Kong%203%20-%20Nazo%20no%20Kremis-tou%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI263" t="inlineStr"/>
       <c r="AJ263" t="inlineStr"/>
       <c r="AK263" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Super%20Donkey%20Kong%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Super%20Donkey%20Kong%203%20-%20Nazo%20no%20Kremis-tou%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL263" t="inlineStr"/>
@@ -57609,7 +57609,7 @@
       </c>
       <c r="AH264" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Ys%20III%20-%20Wanderers%20from%20Ys%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Ys%20III%20-%20Wanderers%20from%20Ys%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI264" t="inlineStr">
@@ -57620,7 +57620,7 @@
       <c r="AJ264" t="inlineStr"/>
       <c r="AK264" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Ys%20III%20-%20Wanderers%20from%20Ys%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Ys%20III%20-%20Wanderers%20from%20Ys%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL264" t="inlineStr"/>
@@ -58891,7 +58891,7 @@
       </c>
       <c r="AH270" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/From%20TV%20Animation%20Slam%20Dunk%20-%20Yonkyou%20Gekitotsu%21%21%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/From%20TV%20Animation%20Slam%20Dunk%20-%20Yonkyou%20Gekitotsu%21%21%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI270" t="inlineStr">
@@ -58906,7 +58906,7 @@
       </c>
       <c r="AK270" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/From%20TV%20Animation%20Slam%20Dunk%20-%20Yonkyou%20Gekitotsu%21%21%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/From%20TV%20Animation%20Slam%20Dunk%20-%20Yonkyou%20Gekitotsu%21%21%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL270" t="inlineStr"/>
@@ -59325,7 +59325,7 @@
       </c>
       <c r="AH272" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Super%20Mario%20World%20%28USA%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Super%20Mario%20World%20-%20Super%20Mario%20Bros.%204%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI272" t="inlineStr">
@@ -59340,7 +59340,7 @@
       </c>
       <c r="AK272" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Super%20Mario%20World%20%28USA%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Super%20Mario%20World%20-%20Super%20Mario%20Bros.%204%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL272" t="inlineStr"/>
@@ -60193,7 +60193,7 @@
       </c>
       <c r="AH276" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Daibakushou%20Jinsei%20Gekijou%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Daibakushou%20Jinsei%20Gekijou%20-%20Dokidoki%20Seishun%20Hen%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI276" t="inlineStr">
@@ -60204,7 +60204,7 @@
       <c r="AJ276" t="inlineStr"/>
       <c r="AK276" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Daibakushou%20Jinsei%20Gekijou%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Daibakushou%20Jinsei%20Gekijou%20-%20Dokidoki%20Seishun%20Hen%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL276" t="inlineStr"/>
@@ -62140,14 +62140,14 @@
       </c>
       <c r="AH285" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/F-1%20Grand%20Prix%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/F-1%20Grand%20Prix%20-%20Part%20II%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI285" t="inlineStr"/>
       <c r="AJ285" t="inlineStr"/>
       <c r="AK285" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/F-1%20Grand%20Prix%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/F-1%20Grand%20Prix%20-%20Part%20II%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL285" t="inlineStr"/>
@@ -63633,7 +63633,7 @@
       </c>
       <c r="AH292" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Sword%20World%20SFC%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Sword%20World%20SFC%202%20-%20Inishie%20no%20Kyojin%20Densetsu%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI292" t="inlineStr">
@@ -63644,7 +63644,7 @@
       <c r="AJ292" t="inlineStr"/>
       <c r="AK292" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Sword%20World%20SFC%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Sword%20World%20SFC%202%20-%20Inishie%20no%20Kyojin%20Densetsu%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL292" t="inlineStr"/>
@@ -64059,7 +64059,7 @@
       </c>
       <c r="AH294" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Torneko%20no%20Daibouken%20-%20Fushigi%20no%20Dungeon%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Torneko%20no%20Daibouken%20-%20Fushigi%20no%20Dungeon%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI294" t="inlineStr">
@@ -64074,7 +64074,7 @@
       </c>
       <c r="AK294" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Torneko%20no%20Daibouken%20-%20Fushigi%20no%20Dungeon%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Torneko%20no%20Daibouken%20-%20Fushigi%20no%20Dungeon%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL294" t="inlineStr"/>
@@ -64919,7 +64919,7 @@
       </c>
       <c r="AH298" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Breath%20of%20Fire%20-%20Ryuu%20no%20Senshi%20%28Japan%29%20%28Rev%201%29%20%28Switch%20Online%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Breath%20of%20Fire%20-%20Ryuu%20no%20Senshi%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI298" t="inlineStr">
@@ -64934,7 +64934,7 @@
       </c>
       <c r="AK298" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Breath%20of%20Fire%20-%20Ryuu%20no%20Senshi%20%28Japan%29%20%28Rev%201%29%20%28Switch%20Online%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Breath%20of%20Fire%20-%20Ryuu%20no%20Senshi%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL298" t="inlineStr"/>
@@ -65795,14 +65795,14 @@
       </c>
       <c r="AH302" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Breath%20of%20Fire%20II%20-%20Shimei%20no%20Ko%20%28Japan%29%20%28Rev%201%29%20%28Virtual%20Console%2C%20Switch%20Online%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Breath%20of%20Fire%20II%20-%20Shimei%20no%20Ko%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI302" t="inlineStr"/>
       <c r="AJ302" t="inlineStr"/>
       <c r="AK302" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Breath%20of%20Fire%20II%20-%20Shimei%20no%20Ko%20%28Japan%29%20%28Rev%201%29%20%28Virtual%20Console%2C%20Switch%20Online%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Breath%20of%20Fire%20II%20-%20Shimei%20no%20Ko%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL302" t="inlineStr"/>
@@ -66444,7 +66444,7 @@
       </c>
       <c r="AH305" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Estpolis%20Denki%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Estpolis%20Denki%20II%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI305" t="inlineStr">
@@ -66455,7 +66455,7 @@
       <c r="AJ305" t="inlineStr"/>
       <c r="AK305" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Estpolis%20Denki%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Estpolis%20Denki%20II%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL305" t="inlineStr"/>
@@ -67515,7 +67515,7 @@
       </c>
       <c r="AH310" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Ganbare%20Goemon%20Kirakira%20Douchuu%20-%20Boku%20ga%20Dancer%20ni%20Natta%20Wake%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Ganbare%20Goemon%20Kirakira%20Douchuu%20-%20Boku%20ga%20Dancer%20ni%20Natta%20Wake%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI310" t="inlineStr">
@@ -67530,7 +67530,7 @@
       </c>
       <c r="AK310" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Ganbare%20Goemon%20Kirakira%20Douchuu%20-%20Boku%20ga%20Dancer%20ni%20Natta%20Wake%20%28Japan%29%20%28Rev%201%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Ganbare%20Goemon%20Kirakira%20Douchuu%20-%20Boku%20ga%20Dancer%20ni%20Natta%20Wake%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL310" t="inlineStr"/>
@@ -68160,7 +68160,7 @@
       </c>
       <c r="AH313" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Ganbare%20Goemon%202%20-%20Kiteretsu%20Shougun%20Magginesu%20%28Japan%29%20%28Virtual%20Console%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Ganbare%20Goemon%202%20-%20Kiteretsu%20Shougun%20Magginesu%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI313" t="inlineStr">
@@ -68171,7 +68171,7 @@
       <c r="AJ313" t="inlineStr"/>
       <c r="AK313" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Ganbare%20Goemon%202%20-%20Kiteretsu%20Shougun%20Magginesu%20%28Japan%29%20%28Virtual%20Console%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Ganbare%20Goemon%202%20-%20Kiteretsu%20Shougun%20Magginesu%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL313" t="inlineStr"/>
@@ -69008,14 +69008,14 @@
       </c>
       <c r="AH317" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Yokoyama%20Mitsuteru%20Sangokushi%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Yokoyama%20Mitsuteru%20Sangokushi%20Bangi%20-%20Sugoroku%20Eiyuu-ki%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AI317" t="inlineStr"/>
       <c r="AJ317" t="inlineStr"/>
       <c r="AK317" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Yokoyama%20Mitsuteru%20Sangokushi%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Snaps/Yokoyama%20Mitsuteru%20Sangokushi%20Bangi%20-%20Sugoroku%20Eiyuu-ki%20%28Japan%29.png</t>
         </is>
       </c>
       <c r="AL317" t="inlineStr"/>

--- a/data/RetroVault_GS_Games_全量匯入檔.xlsx
+++ b/data/RetroVault_GS_Games_全量匯入檔.xlsx
@@ -10180,12 +10180,12 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Nintendo_Entertainment_System/master/Named_Boxarts/Urban%20Champion%20(World).png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/fc_urban_champion_jp_front.jpg</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/d3bb536b-9aca-423b-865e-f07261592f24.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/fc_urban_champion_jp_back.jpg</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Nintendo_Entertainment_System/master/Named_Boxarts/Excitebike%20(Japan%2C%20USA)%20(En).png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/fc_excitebike_jp_front.jpg</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/2f5e8f0f-645d-4a8e-8736-4f15090ce6bb.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/fc_excitebike_jp_back.jpg</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -15408,12 +15408,12 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Nintendo_Entertainment_System/master/Named_Boxarts/Dr.%20Mario%20(Japan%2C%20USA)%20(En).png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/fc_dr_mario_jp_front.png</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/8738eba1-ed19-4784-8268-f0dfe69b7a41.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/fc_dr_mario_jp_back.jpg</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -19979,12 +19979,12 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Nintendo_Entertainment_System/master/Named_Boxarts/Super%20Mario%20Bros.%20(World).png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/fc_super_mario_bros_jp_front.jpg</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/2f4409b2-6c02-4839-a7ae-31e14fce1bde.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/fc_super_mario_bros_jp_back.jpg</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">

--- a/data/RetroVault_GS_Games_全量匯入檔.xlsx
+++ b/data/RetroVault_GS_Games_全量匯入檔.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RetroVault_Games" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Games" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -71126,11 +71126,19 @@
       </c>
       <c r="AH327" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Game_Boy/master/Named_Boxarts/Quarth%20%28Japan%29.png</t>
-        </is>
-      </c>
-      <c r="AI327" t="inlineStr"/>
-      <c r="AJ327" t="inlineStr"/>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_quarth_jp_front.jpg</t>
+        </is>
+      </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_quarth_jp_back.jpg</t>
+        </is>
+      </c>
+      <c r="AJ327" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_quarth_jp_spine.jpg</t>
+        </is>
+      </c>
       <c r="AK327" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Game_Boy/master/Named_Snaps/Quarth%20%28Japan%29.png</t>
@@ -71337,11 +71345,19 @@
       </c>
       <c r="AH328" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Game_Boy/master/Named_Boxarts/Hokuto%20no%20Ken%20-%20Seizetsu%20Juuban%20Shoubu%20%28Japan%29.png</t>
-        </is>
-      </c>
-      <c r="AI328" t="inlineStr"/>
-      <c r="AJ328" t="inlineStr"/>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_hokuto_jp_front.jpg</t>
+        </is>
+      </c>
+      <c r="AI328" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_hokuto_jp_back.jpg</t>
+        </is>
+      </c>
+      <c r="AJ328" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_hokuto_jp_spine.jpg</t>
+        </is>
+      </c>
       <c r="AK328" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Game_Boy/master/Named_Snaps/Hokuto%20no%20Ken%20-%20Seizetsu%20Juuban%20Shoubu%20%28Japan%29.png</t>
@@ -71759,10 +71775,14 @@
       </c>
       <c r="AH330" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Game_Boy/master/Named_Boxarts/Nekketsu%20Koukou%20Soccer-bu%20-%20World%20Cup%20Hen%20%28Japan%29.png</t>
-        </is>
-      </c>
-      <c r="AI330" t="inlineStr"/>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_nekketsu_soccer_jp_front.jpg</t>
+        </is>
+      </c>
+      <c r="AI330" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_nekketsu_soccer_jp_back.jpg</t>
+        </is>
+      </c>
       <c r="AJ330" t="inlineStr"/>
       <c r="AK330" t="inlineStr">
         <is>
@@ -71970,11 +71990,19 @@
       </c>
       <c r="AH331" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Game_Boy/master/Named_Boxarts/Nobunaga%20no%20Yabou%20-%20Game%20Boy%20Ban%20%28Japan%29.png</t>
-        </is>
-      </c>
-      <c r="AI331" t="inlineStr"/>
-      <c r="AJ331" t="inlineStr"/>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_nobunaga_jp_front.jpg</t>
+        </is>
+      </c>
+      <c r="AI331" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_nobunaga_jp_back.jpg</t>
+        </is>
+      </c>
+      <c r="AJ331" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_nobunaga_jp_spine.jpg</t>
+        </is>
+      </c>
       <c r="AK331" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Game_Boy/master/Named_Snaps/Nobunaga%20no%20Yabou%20-%20Game%20Boy%20Ban%20%28Japan%29.png</t>
@@ -72603,10 +72631,14 @@
       </c>
       <c r="AH334" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Game_Boy/master/Named_Boxarts/Boxing%20%28Japan%29.png</t>
-        </is>
-      </c>
-      <c r="AI334" t="inlineStr"/>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_boxing_jp_front.png</t>
+        </is>
+      </c>
+      <c r="AI334" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_boxing_jp_back.jpg</t>
+        </is>
+      </c>
       <c r="AJ334" t="inlineStr"/>
       <c r="AK334" t="inlineStr">
         <is>
@@ -73244,11 +73276,19 @@
       </c>
       <c r="AH337" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Game_Boy/master/Named_Boxarts/R-Type%20%28Japan%29.png</t>
-        </is>
-      </c>
-      <c r="AI337" t="inlineStr"/>
-      <c r="AJ337" t="inlineStr"/>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_rtype_jp_front.png</t>
+        </is>
+      </c>
+      <c r="AI337" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_rtype_jp_back.png</t>
+        </is>
+      </c>
+      <c r="AJ337" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gb_rtype_jp_spine.png</t>
+        </is>
+      </c>
       <c r="AK337" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Game_Boy/master/Named_Snaps/R-Type%20%28Japan%29.png</t>
@@ -74096,14 +74136,14 @@
       </c>
       <c r="AH341" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Sega_-_Game_Gear/master/Named_Boxarts/Sonic%20_%20Tails%202%20%28Japan%29%20%28En%29.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gg_sonic_tails_1_jp_front.png</t>
         </is>
       </c>
       <c r="AI341" t="inlineStr"/>
       <c r="AJ341" t="inlineStr"/>
       <c r="AK341" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Sega_-_Game_Gear/master/Named_Snaps/Sonic%20_%20Tails%202%20%28Japan%29%20%28En%29.png</t>
+          <t>https://raw.githubusercontent.com/libretro-thumbnails/Sega_-_Game_Gear/master/Named_Snaps/Sonic%20_%20Tails%20(Japan)%20(En).png</t>
         </is>
       </c>
       <c r="AL341" t="inlineStr"/>
@@ -76918,22 +76958,22 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>ピノビィの大冒険</t>
+          <t>ピノビィーの大冒険</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>ピノビィの大冒険</t>
+          <t>ピノビィーの大冒険</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>皮諾比大冒險</t>
+          <t>皮諾比的大冒險</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Pinobee: Wings of Adventure</t>
+          <t>Pinobee: Quest of Heart</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -77058,7 +77098,7 @@
       </c>
       <c r="AH355" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Game_Boy_Advance/master/Named_Boxarts/Pinobee%20no%20Daibouken%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gba_pinobee_jp_front.jpg</t>
         </is>
       </c>
       <c r="AI355" t="inlineStr"/>
@@ -79588,7 +79628,11 @@
           <t>https://www.google.com/search?q=UP%20USB%20CARD%20256M%20Game%20Boy%20Advance</t>
         </is>
       </c>
-      <c r="AH367" t="inlineStr"/>
+      <c r="AH367" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/gba_up_usb_card_256m.jpg</t>
+        </is>
+      </c>
       <c r="AI367" t="inlineStr"/>
       <c r="AJ367" t="inlineStr"/>
       <c r="AK367" t="inlineStr"/>

--- a/data/RetroVault_GS_Games_全量匯入檔.xlsx
+++ b/data/RetroVault_GS_Games_全量匯入檔.xlsx
@@ -8957,17 +8957,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>桃太郎活劇</t>
+          <t>桃太郎電鉄</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>桃太郎活劇</t>
+          <t>桃太郎電鉄</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>桃太郎活劇</t>
+          <t>桃太郎電鐵</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -36014,7 +36014,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/7bd36c35-ba0e-4352-91a0-68184df3e5ee.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/sfc_teitoku_jp_back.jpg</t>
         </is>
       </c>
       <c r="AJ164" t="inlineStr"/>
@@ -36227,11 +36227,7 @@
           <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Teitoku%20no%20Ketsudan%20II%20%28Japan%29.png</t>
         </is>
       </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/76d52e61-4bb3-4e7f-bfc4-abc4cf49cb2a.jpg</t>
-        </is>
-      </c>
+      <c r="AI165" t="inlineStr"/>
       <c r="AJ165" t="inlineStr"/>
       <c r="AK165" t="inlineStr">
         <is>
@@ -36657,11 +36653,7 @@
           <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Super%20Nobunaga%20no%20Yabou%20-%20Bushou%20Fuuunroku%20%28Japan%29.png</t>
         </is>
       </c>
-      <c r="AI167" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/82d0864d-90f1-4f8a-abad-db3b25533533.jpg</t>
-        </is>
-      </c>
+      <c r="AI167" t="inlineStr"/>
       <c r="AJ167" t="inlineStr"/>
       <c r="AK167" t="inlineStr">
         <is>
@@ -36874,7 +36866,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/eabf6d84-263e-4c7c-a063-daccfbfb1826.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/sfc_kouryuuki_jp_back.jpg</t>
         </is>
       </c>
       <c r="AJ168" t="inlineStr"/>
@@ -42038,7 +42030,7 @@
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/857ba3b4-74e0-4879-aa2a-1a5638af1163.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/sfc_bahamut_lagoon_jp_back.jpg</t>
         </is>
       </c>
       <c r="AJ192" t="inlineStr">
@@ -43117,7 +43109,7 @@
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/82d0864d-90f1-4f8a-abad-db3b25533533.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/sfc_nobunaga_zenkoku_jp_back.jpg</t>
         </is>
       </c>
       <c r="AJ197" t="inlineStr"/>
@@ -44836,12 +44828,12 @@
       </c>
       <c r="AH205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Teitoku%20no%20Ketsudan%20%28Japan%29.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/sfc_teitoku_reprint_jp_front.png</t>
         </is>
       </c>
       <c r="AI205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/7bd36c35-ba0e-4352-91a0-68184df3e5ee.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/sfc_teitoku_jp_back.jpg</t>
         </is>
       </c>
       <c r="AJ205" t="inlineStr"/>
@@ -45051,10 +45043,14 @@
       </c>
       <c r="AH206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/libretro-thumbnails/Nintendo_-_Super_Nintendo_Entertainment_System/master/Named_Boxarts/Super%20Sangokushi%20II%20%28Japan%29.png</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr"/>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/sfc_super_sangokushi2_reprint_jp_front.png</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/sfc_super_sangokushi2_reprint_jp_back.png</t>
+        </is>
+      </c>
       <c r="AJ206" t="inlineStr"/>
       <c r="AK206" t="inlineStr">
         <is>
@@ -53067,7 +53063,7 @@
       </c>
       <c r="AI243" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/6aebd916-c066-4c45-82a0-34378bd15990.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/sfc_fe_monshou_jp_back.jpg</t>
         </is>
       </c>
       <c r="AJ243" t="inlineStr"/>
@@ -53282,7 +53278,7 @@
       </c>
       <c r="AI244" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/137b3f22-c980-4ee3-b9cd-b8a5ab10436f.png</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/sfc_fe_seisen_jp_back.jpg</t>
         </is>
       </c>
       <c r="AJ244" t="inlineStr"/>
@@ -60413,7 +60409,7 @@
       </c>
       <c r="AI277" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/2906c1fc-0532-488e-af4c-c0e8d08b2012.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/sfc_space_invaders_jp_back.jpg</t>
         </is>
       </c>
       <c r="AJ277" t="inlineStr">
@@ -64924,7 +64920,7 @@
       </c>
       <c r="AI298" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/92109d5b-d550-40d8-8545-e5af8aea4d3f.jpg</t>
+          <t>https://raw.githubusercontent.com/Kevinte67228/Retro-library/main/docs/cdn/sfc_breath_of_fire_jp_back.jpg</t>
         </is>
       </c>
       <c r="AJ298" t="inlineStr">
